--- a/tests/realSuite/piano_trasporti_Calcio-a-5_IC_18-mar-26_CON-VETTORI-3/input.xlsx
+++ b/tests/realSuite/piano_trasporti_Calcio-a-5_IC_18-mar-26_CON-VETTORI-3/input.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ala, Via Betta 9</t>
+          <t>Scuola primaria "Abramo Betta", 9, Via Abramo Betta, Ala, Comunità della Vallagarina, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38061, Italia</t>
         </is>
       </c>
       <c r="C2" t="n">

--- a/tests/realSuite/piano_trasporti_Calcio-a-5_IC_18-mar-26_CON-VETTORI-3/input.xlsx
+++ b/tests/realSuite/piano_trasporti_Calcio-a-5_IC_18-mar-26_CON-VETTORI-3/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC ALDENO MATTARELLO</t>
+          <t>IC CENTRO VALSUGANA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aldeno, Via Filzi</t>
+          <t>Roncegno, Via C. Battisti (rist. Al Picchio)</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -466,12 +466,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC ALDENO MATTARELLO</t>
+          <t>IC CENTRO VALSUGANA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mattarello, Via della Torre Franca</t>
+          <t>Telve, Piazza Maggiore</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -481,42 +481,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC ALTA VALLAGARINA</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fermate Bus di linea della SS12 per Volano, Calliano (centro) e Besenello di fronte alla scuola elementare in Via Degasperi</t>
+          <t>Pieve di Bono-Prezzo, Via Fiera</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC ALTA VALLAGARINA</t>
+          <t>IC CHIESE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Roveto, Piazzale Orsi</t>
+          <t>Storo, Via Papaleoni 5</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC CENTRO VALSUGANA</t>
+          <t>IC FOLGARIA LAVARONE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Roncegno, Via C. Battisti (rist. Al Picchio)</t>
+          <t>Folgaria, Parcheggio Palaghiaccio</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -526,12 +526,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC CENTRO VALSUGANA</t>
+          <t>IC FOLGARIA LAVARONE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Telve, Piazza Maggiore</t>
+          <t>Lavarone, Frazione Gionghi 107/6</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -541,42 +541,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC CHIESE</t>
+          <t>IC FONDO REVO’</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pieve di Bono-Prezzo, Via Fiera</t>
+          <t>Borgo D’Anaunia, Via Zambotti, 24</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC CHIESE</t>
+          <t>IC GIUDICARIE ESTERIORI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storo, Via Papaleoni 5</t>
+          <t>Comano Terme, Via S. Giovanni Bosco</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC FOLGARIA LAVARONE</t>
+          <t>IC ISERA ROVERETO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Folgaria, Parcheggio Palaghiaccio</t>
+          <t>Rovereto, Viale della Vittoria 43</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -586,117 +586,117 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC FOLGARIA LAVARONE</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lavarone, Frazione Gionghi 107/6</t>
+          <t>Campitello - Strada de Marin, 3/A</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC FONDO REVO’</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Borgo D’Anaunia, Via Zambotti, 24</t>
+          <t>Moena, Fermata Hotel Trentino</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC GIUDICARIE ESTERIORI</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Comano Terme, Via S. Giovanni Bosco</t>
+          <t>San Jan - Strada Dolomites - Pozza di Fassa, 67</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC ISERA ROVERETO</t>
+          <t>IC MORI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rovereto, Viale della Vittoria 43</t>
+          <t>Mori, Via Giovanni XXIII, 64</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Campitello - Strada de Marin, 3/A</t>
+          <t>Pergine, Via dei Caduti 39</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC ROVERETO NORD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Moena, Fermata Hotel Trentino</t>
+          <t>Rovereto Corso Bettini, 67</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC STRIGNO TESINO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>San Jan - Strada Dolomites - Pozza di Fassa, 67</t>
+          <t>Strigno, Castello Ivano, Via Roma 14</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IC MORI</t>
+          <t>IC TAIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mori, Via Giovanni XXIII, 64</t>
+          <t>Taio, Piazza dalla Chiesa</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -706,27 +706,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC VALLE DEI LAGHI - DRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pergine, Via dei Caduti 39</t>
+          <t>Cavedine, Piazza Italia</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC ROVERETO NORD</t>
+          <t>IC VALLE DEI LAGHI - DRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rovereto Corso Bettini, 67</t>
+          <t>Dro, Via S. Antonio</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -736,75 +736,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC STRIGNO TESINO</t>
+          <t>IC VALLE DEI LAGHI - DRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Strigno, Castello Ivano, Via Roma 14</t>
+          <t>Vezzano, Via Roma 3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>IC TAIO</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Taio, Piazza dalla Chiesa</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>IC VALLE DEI LAGHI - DRO</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Cavedine, Piazza Italia</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>IC VALLE DEI LAGHI - DRO</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Dro, Via S. Antonio</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>IC VALLE DEI LAGHI - DRO</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Vezzano, Via Roma 3</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
         <v>5</v>
       </c>
     </row>
